--- a/Hardware/Hardware.xlsx
+++ b/Hardware/Hardware.xlsx
@@ -16,23 +16,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Preisliste Hardware</t>
   </si>
   <si>
+    <t>Menge</t>
+  </si>
+  <si>
     <t>Hardware</t>
   </si>
   <si>
     <t>Links</t>
   </si>
   <si>
-    <t>Preis</t>
+    <t xml:space="preserve">Preis (nach Menge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2 x</t>
   </si>
   <si>
     <t xml:space="preserve">ESP 32</t>
   </si>
   <si>
+    <t>https://www.amazon.de/dp/B0DHRV7784</t>
+  </si>
+  <si>
     <t xml:space="preserve">Strom / Spannung</t>
   </si>
   <si>
@@ -51,6 +60,9 @@
     <t>https://www.amazon.de/dp/B0C3VC5H6M</t>
   </si>
   <si>
+    <t xml:space="preserve">1/3 x</t>
+  </si>
+  <si>
     <t>Schallsensor</t>
   </si>
   <si>
@@ -63,22 +75,43 @@
     <t>Lichtschranke</t>
   </si>
   <si>
+    <t xml:space="preserve">1 x</t>
+  </si>
+  <si>
     <t xml:space="preserve">RJ45 (Pack of 7)</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0F4MWBK5H</t>
   </si>
   <si>
-    <t xml:space="preserve">RJ45 Cable</t>
+    <t xml:space="preserve">2 x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RJ45 Cable </t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B00N2VILDM</t>
   </si>
   <si>
+    <t xml:space="preserve">Jumper Cable (40)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/dp/B07KYHBVR7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/5 x</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLA (200g)</t>
   </si>
   <si>
     <t>https://www.amazon.de/dp/B0BTHSVQ89/</t>
+  </si>
+  <si>
+    <t>Schrauben</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/dp/B0GF13W3SL</t>
   </si>
 </sst>
 </file>
@@ -126,12 +159,34 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -146,12 +201,14 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -164,13 +221,11 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
         <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
+      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -178,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -187,11 +242,14 @@
     <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="3" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="3" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,8 +751,8 @@
   <cols>
     <col min="1" max="2" style="1" width="9.140625"/>
     <col customWidth="1" min="3" max="3" style="1" width="18.28125"/>
-    <col customWidth="1" min="4" max="4" style="1" width="36.57421875"/>
-    <col customWidth="1" min="5" max="5" style="1" width="18.140625"/>
+    <col customWidth="1" min="4" max="4" style="1" width="45.8515625"/>
+    <col customWidth="1" min="5" max="5" style="1" width="20.28125"/>
     <col min="6" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
@@ -706,241 +764,302 @@
       <c r="E5" s="2"/>
     </row>
     <row r="7" ht="18">
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" ht="18">
-      <c r="C8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="9">
         <v>5.4900000000000002</v>
       </c>
     </row>
     <row r="9" ht="18">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="18">
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="C10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="9">
         <v>2.9900000000000002</v>
       </c>
     </row>
     <row r="11" ht="18">
-      <c r="C11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="B11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="9">
         <v>5.0899999999999999</v>
       </c>
     </row>
     <row r="12" ht="18">
-      <c r="C12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="B12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="9">
         <v>4.4900000000000002</v>
       </c>
     </row>
     <row r="13" ht="18">
-      <c r="C13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="9">
         <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="14" ht="18">
-      <c r="C14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
+      <c r="B14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" ht="18">
-      <c r="C15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" ht="18">
-      <c r="C16" s="5"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" ht="18">
-      <c r="C17" s="5"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" ht="18">
-      <c r="C18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="B18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="9">
         <v>8.9900000000000002</v>
       </c>
     </row>
     <row r="19" ht="18">
-      <c r="C19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1.99</v>
+      <c r="B19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.98</v>
       </c>
     </row>
     <row r="20" ht="18">
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2.4900000000000002</v>
+      </c>
     </row>
     <row r="21" ht="18">
-      <c r="C21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="B21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="9">
         <v>2.9900000000000002</v>
       </c>
     </row>
     <row r="22" ht="18">
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="9"/>
+      <c r="B22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="12">
+        <v>2.4900000000000002</v>
+      </c>
     </row>
     <row r="23" ht="18">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6">
+      <c r="B23" s="13"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="9">
         <f>SUM(E8:E22)</f>
-        <v>34.520000000000003</v>
+        <v>41.490000000000009</v>
       </c>
     </row>
     <row r="24" ht="18">
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" ht="18">
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" ht="18">
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" ht="18">
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" ht="18">
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" ht="18">
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" ht="18">
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
     </row>
     <row r="31" ht="18">
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
     </row>
     <row r="32" ht="18">
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
     </row>
     <row r="33" ht="18">
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
     </row>
     <row r="34" ht="18">
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
     </row>
     <row r="35" ht="18">
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
     </row>
     <row r="36" ht="18">
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
     </row>
     <row r="37" ht="18">
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
     </row>
     <row r="38" ht="18">
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
     </row>
     <row r="39" ht="18">
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C5:E5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="D10"/>
-    <hyperlink r:id="rId2" ref="D11"/>
-    <hyperlink r:id="rId3" ref="D12"/>
-    <hyperlink r:id="rId4" ref="D13"/>
-    <hyperlink r:id="rId5" ref="D18"/>
-    <hyperlink r:id="rId6" ref="D19"/>
-    <hyperlink r:id="rId7" ref="D21"/>
+    <hyperlink r:id="rId1" ref="D8"/>
+    <hyperlink r:id="rId2" ref="D10"/>
+    <hyperlink r:id="rId3" ref="D11"/>
+    <hyperlink r:id="rId4" ref="D12"/>
+    <hyperlink r:id="rId5" ref="D13"/>
+    <hyperlink r:id="rId6" ref="D18"/>
+    <hyperlink r:id="rId7" ref="D19"/>
+    <hyperlink r:id="rId8" ref="D20"/>
+    <hyperlink r:id="rId9" ref="D21"/>
+    <hyperlink r:id="rId10" ref="D22"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
